--- a/training_program.xlsx
+++ b/training_program.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kamadakotaro/Dropbox/SR渋谷/training_log_app/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C6A3921-B968-E243-8C79-8831A7D185D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0803857-C10B-8941-AB46-3CC59A1ED2EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="17080" xr2:uid="{2078C720-DD1B-E243-A1C1-2D8E856581F3}"/>
+    <workbookView xWindow="0" yWindow="720" windowWidth="14580" windowHeight="18400" xr2:uid="{2078C720-DD1B-E243-A1C1-2D8E856581F3}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1040" uniqueCount="210">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1093" uniqueCount="231">
   <si>
     <t xml:space="preserve">Program </t>
     <phoneticPr fontId="1"/>
@@ -939,6 +939,102 @@
   </si>
   <si>
     <t>Lower</t>
+  </si>
+  <si>
+    <t>U15オフ期間 Day1（7.31-）</t>
+  </si>
+  <si>
+    <t>U15オフ期間 Day1（7.31-）</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>プランク（キープ）+アームリーチ</t>
+  </si>
+  <si>
+    <t>ラテラルホップ（連続）</t>
+  </si>
+  <si>
+    <t>ワイドスクワット</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Vシット</t>
+  </si>
+  <si>
+    <t>1000m走</t>
+  </si>
+  <si>
+    <t>30sec+10</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>2本</t>
+    <rPh sb="1" eb="2">
+      <t>ホn</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>U15オフ期間 Day2（7.31-）</t>
+  </si>
+  <si>
+    <t>U15オフ期間 Day2（7.31-）</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>サイドプランク+アブダクション</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>スプリットSQ（キープ）</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>1LRDL</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>目標3分50秒以内</t>
+    <rPh sb="0" eb="2">
+      <t>モクヒョウ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>プn</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ビョウ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ビョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>3ea</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>20ea</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>インターバル走</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>2set</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>120m(22秒)+休憩(44秒)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>10本</t>
+    <rPh sb="2" eb="3">
+      <t>ホn</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
   </si>
 </sst>
 </file>
@@ -1337,7 +1433,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5699522-EC18-EB4A-B86B-9AA898F17175}">
-  <dimension ref="A1:H242"/>
+  <dimension ref="A1:H256"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
   <cols>
     <col min="1" max="1" width="25.140625" bestFit="1" customWidth="1"/>
@@ -6520,6 +6616,285 @@
         <v>206</v>
       </c>
     </row>
+    <row r="243" spans="1:8">
+      <c r="A243" t="s">
+        <v>211</v>
+      </c>
+      <c r="B243" s="2">
+        <v>1</v>
+      </c>
+      <c r="C243" t="s">
+        <v>212</v>
+      </c>
+      <c r="D243">
+        <v>2</v>
+      </c>
+      <c r="E243" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F243" s="2" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="244" spans="1:8">
+      <c r="A244" t="s">
+        <v>211</v>
+      </c>
+      <c r="B244" s="2">
+        <v>2</v>
+      </c>
+      <c r="C244" t="s">
+        <v>96</v>
+      </c>
+      <c r="D244">
+        <v>2</v>
+      </c>
+      <c r="E244" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F244" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="245" spans="1:8">
+      <c r="A245" t="s">
+        <v>210</v>
+      </c>
+      <c r="B245" s="2">
+        <v>3</v>
+      </c>
+      <c r="C245" t="s">
+        <v>213</v>
+      </c>
+      <c r="D245">
+        <v>3</v>
+      </c>
+      <c r="E245" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F245" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="246" spans="1:8">
+      <c r="A246" t="s">
+        <v>210</v>
+      </c>
+      <c r="B246" s="2">
+        <v>4</v>
+      </c>
+      <c r="C246" t="s">
+        <v>214</v>
+      </c>
+      <c r="D246">
+        <v>3</v>
+      </c>
+      <c r="E246" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F246" s="2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="247" spans="1:8">
+      <c r="A247" t="s">
+        <v>210</v>
+      </c>
+      <c r="B247" s="2">
+        <v>5</v>
+      </c>
+      <c r="C247" t="s">
+        <v>98</v>
+      </c>
+      <c r="D247">
+        <v>3</v>
+      </c>
+      <c r="E247" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F247">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="248" spans="1:8">
+      <c r="A248" t="s">
+        <v>210</v>
+      </c>
+      <c r="B248" s="2">
+        <v>6</v>
+      </c>
+      <c r="C248" t="s">
+        <v>215</v>
+      </c>
+      <c r="D248">
+        <v>3</v>
+      </c>
+      <c r="E248" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F248" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="249" spans="1:8">
+      <c r="A249" t="s">
+        <v>210</v>
+      </c>
+      <c r="B249" s="4">
+        <v>7</v>
+      </c>
+      <c r="C249" t="s">
+        <v>216</v>
+      </c>
+      <c r="D249" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="E249" s="2"/>
+      <c r="F249" s="2"/>
+      <c r="G249" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="250" spans="1:8">
+      <c r="A250" t="s">
+        <v>220</v>
+      </c>
+      <c r="B250" s="2">
+        <v>1</v>
+      </c>
+      <c r="C250" t="s">
+        <v>221</v>
+      </c>
+      <c r="D250">
+        <v>2</v>
+      </c>
+      <c r="E250" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F250" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="251" spans="1:8">
+      <c r="A251" t="s">
+        <v>220</v>
+      </c>
+      <c r="B251" s="4">
+        <v>2</v>
+      </c>
+      <c r="C251" t="s">
+        <v>222</v>
+      </c>
+      <c r="D251">
+        <v>3</v>
+      </c>
+      <c r="E251" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F251" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="252" spans="1:8">
+      <c r="A252" t="s">
+        <v>219</v>
+      </c>
+      <c r="B252" s="2">
+        <v>3</v>
+      </c>
+      <c r="C252" t="s">
+        <v>147</v>
+      </c>
+      <c r="D252">
+        <v>3</v>
+      </c>
+      <c r="E252" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F252" s="2" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="253" spans="1:8">
+      <c r="A253" t="s">
+        <v>219</v>
+      </c>
+      <c r="B253" s="2">
+        <v>4</v>
+      </c>
+      <c r="C253" t="s">
+        <v>75</v>
+      </c>
+      <c r="D253">
+        <v>3</v>
+      </c>
+      <c r="E253" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F253" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="254" spans="1:8">
+      <c r="A254" t="s">
+        <v>219</v>
+      </c>
+      <c r="B254" s="4">
+        <v>5</v>
+      </c>
+      <c r="C254" t="s">
+        <v>223</v>
+      </c>
+      <c r="D254">
+        <v>3</v>
+      </c>
+      <c r="E254" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F254" s="2" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="255" spans="1:8">
+      <c r="A255" t="s">
+        <v>219</v>
+      </c>
+      <c r="B255" s="2">
+        <v>6</v>
+      </c>
+      <c r="C255" t="s">
+        <v>99</v>
+      </c>
+      <c r="D255">
+        <v>3</v>
+      </c>
+      <c r="E255" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F255" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="256" spans="1:8">
+      <c r="A256" t="s">
+        <v>219</v>
+      </c>
+      <c r="B256" s="2">
+        <v>7</v>
+      </c>
+      <c r="C256" t="s">
+        <v>227</v>
+      </c>
+      <c r="D256" t="s">
+        <v>228</v>
+      </c>
+      <c r="E256" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="F256" s="2" t="s">
+        <v>230</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:G242" xr:uid="{F5699522-EC18-EB4A-B86B-9AA898F17175}"/>
   <phoneticPr fontId="1"/>
